--- a/research/traditional_assets/database/data/bermuda/bermuda_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_retail_special_lines.xlsx
@@ -645,10 +645,10 @@
         <v>0.3732349573845566</v>
       </c>
       <c r="X2">
-        <v>0.1197500112451954</v>
+        <v>0.1197197246070414</v>
       </c>
       <c r="Y2">
-        <v>0.2534849461393613</v>
+        <v>0.2535152327775153</v>
       </c>
       <c r="Z2">
         <v>3.297681031034511</v>
@@ -657,10 +657,10 @@
         <v>0.3144417076243857</v>
       </c>
       <c r="AB2">
-        <v>0.1065974628381271</v>
+        <v>0.1065756034413341</v>
       </c>
       <c r="AC2">
-        <v>0.2078442447862585</v>
+        <v>0.2078661041830516</v>
       </c>
       <c r="AD2">
         <v>253</v>
@@ -776,10 +776,10 @@
         <v>0.3732349573845566</v>
       </c>
       <c r="X3">
-        <v>0.1197500112451954</v>
+        <v>0.1197197246070414</v>
       </c>
       <c r="Y3">
-        <v>0.2534849461393613</v>
+        <v>0.2535152327775153</v>
       </c>
       <c r="Z3">
         <v>3.297681031034511</v>
@@ -788,10 +788,10 @@
         <v>0.3144417076243857</v>
       </c>
       <c r="AB3">
-        <v>0.1065974628381271</v>
+        <v>0.1065756034413341</v>
       </c>
       <c r="AC3">
-        <v>0.2078442447862585</v>
+        <v>0.2078661041830516</v>
       </c>
       <c r="AD3">
         <v>253</v>
